--- a/sitepreview/trust/StructureDefinition-CWT.xlsx
+++ b/sitepreview/trust/StructureDefinition-CWT.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-05-19T11:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -861,7 +861,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>80</v>
@@ -936,7 +936,7 @@
         <v>79</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>80</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>80</v>
@@ -1039,7 +1039,7 @@
         <v>84</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>80</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>80</v>
@@ -1142,7 +1142,7 @@
         <v>88</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>80</v>
